--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29497.97</v>
+        <v>29308.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4328.97</v>
+        <v>4310.32</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12947.67</v>
+        <v>12760.36</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5791.89</v>
+        <v>5667.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5605.05</v>
+        <v>5474.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/mar-2026.xlsx
@@ -749,7 +749,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
